--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486972_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486972_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8922</v>
+        <v>7.2088</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5856</v>
+        <v>3.3764</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3066</v>
+        <v>3.8323</v>
       </c>
       <c r="G2" t="n">
         <v>2.9406</v>
@@ -610,13 +610,13 @@
         <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2256</v>
+        <v>1.5421</v>
       </c>
       <c r="T2" t="n">
-        <v>0.209</v>
+        <v>-0.0002</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0166</v>
+        <v>1.5423</v>
       </c>
       <c r="V2" t="n">
         <v>1.0833</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4279</v>
+        <v>4.0943</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4604</v>
+        <v>1.6822</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9675</v>
+        <v>2.4121</v>
       </c>
       <c r="G3" t="n">
         <v>4.3976</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1749</v>
+        <v>1.8413</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4328</v>
+        <v>0.6546</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7421</v>
+        <v>1.1867</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7072000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0328</v>
+        <v>3.0059</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3079</v>
+        <v>-0.2151</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7249</v>
+        <v>3.221</v>
       </c>
       <c r="G4" t="n">
         <v>1.394</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0504</v>
+        <v>2.0234</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7746</v>
+        <v>0.2516</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2757</v>
+        <v>1.7718</v>
       </c>
       <c r="V4" t="n">
         <v>0.8205</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2138</v>
+        <v>2.0482</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8194</v>
+        <v>1.5056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3944</v>
+        <v>0.5426</v>
       </c>
       <c r="G5" t="n">
         <v>1.2824</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2537</v>
+        <v>0.0881</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4339</v>
+        <v>0.1201</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1801</v>
+        <v>-0.0319</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3491</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1363</v>
+        <v>1.3002</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2624</v>
+        <v>1.367</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.126</v>
+        <v>-0.0668</v>
       </c>
       <c r="G6" t="n">
         <v>1.0968</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0395</v>
+        <v>0.2034</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1046</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.231</v>
+        <v>0.4001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3841</v>
+        <v>1.2151</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6151</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5457</v>
       </c>
       <c r="H7" t="n">
-        <v>1.304</v>
+        <v>2.6016</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8549</v>
+        <v>-3.1473</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4722</v>
+        <v>0.5717</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0512</v>
+        <v>2.3748</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.579</v>
+        <v>-1.8031</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0231</v>
+        <v>-1.1174</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2528</v>
+        <v>0.2268</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2759</v>
+        <v>-1.3441</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R7" t="n">
         <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3712</v>
+        <v>0.77</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1704</v>
+        <v>0.0192</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2008</v>
+        <v>0.7508</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0563</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.8858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8081</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2737</v>
+        <v>-0.4887</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0818</v>
+        <v>0.5558</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5457</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6016</v>
+        <v>1.304</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.1473</v>
+        <v>-1.8549</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5717</v>
+        <v>0.4722</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3748</v>
+        <v>1.0512</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8031</v>
+        <v>-0.579</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1174</v>
+        <v>-1.0231</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2268</v>
+        <v>0.2528</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3441</v>
+        <v>-1.2759</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4382</v>
+        <v>0.2073</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9222</v>
+        <v>0.0658</v>
       </c>
       <c r="U8" t="n">
-        <v>0.484</v>
+        <v>0.1415</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0563</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6552</v>
+        <v>-0.4609</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6486</v>
+        <v>-3.6026</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9935</v>
+        <v>3.1417</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1283</v>
@@ -1156,13 +1156,13 @@
         <v>2.8748</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3351</v>
+        <v>0.8592</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4492</v>
+        <v>-0.4032</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1141</v>
+        <v>1.2623</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5758</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3501</v>
+        <v>-1.5429</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7412</v>
+        <v>-2.9043</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3911</v>
+        <v>1.3614</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9696</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.167</v>
+        <v>0.6402</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1857</v>
+        <v>-0.3489</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0187</v>
+        <v>0.9891</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>16.1206</v>
+        <v>16.1208</v>
       </c>
       <c r="E11" t="n">
-        <v>1.935499999999998</v>
+        <v>1.9356</v>
       </c>
       <c r="F11" t="n">
-        <v>14.1853</v>
+        <v>14.1851</v>
       </c>
       <c r="G11" t="n">
         <v>6.9169</v>
@@ -1315,10 +1315,10 @@
         <v>8.174999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4635999999999998</v>
+        <v>0.4636</v>
       </c>
       <c r="U11" t="n">
-        <v>7.7114</v>
+        <v>7.711399999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0248</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.5097</v>
+        <v>7.0634</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7113</v>
+        <v>6.5021</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7984</v>
+        <v>0.5613</v>
       </c>
       <c r="G12" t="n">
         <v>6.3922</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9872</v>
+        <v>-1.4335</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0812</v>
+        <v>-1.2904</v>
       </c>
       <c r="U12" t="n">
-        <v>0.094</v>
+        <v>-0.1431</v>
       </c>
       <c r="V12" t="n">
         <v>1.4887</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3696</v>
+        <v>2.4445</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3386</v>
+        <v>0.4432</v>
       </c>
       <c r="F13" t="n">
-        <v>2.031</v>
+        <v>2.0013</v>
       </c>
       <c r="G13" t="n">
         <v>1.4935</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8489</v>
+        <v>-0.7739</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1198</v>
+        <v>-1.0152</v>
       </c>
       <c r="U13" t="n">
-        <v>0.271</v>
+        <v>0.2413</v>
       </c>
       <c r="V13" t="n">
         <v>0.2875</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2445</v>
+        <v>0.024</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0473</v>
+        <v>0.1619</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1971</v>
+        <v>-0.1378</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3618</v>
@@ -1546,13 +1546,13 @@
         <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.437</v>
+        <v>-0.1685</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.527</v>
+        <v>-0.3178</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1492</v>
       </c>
       <c r="V14" t="n">
         <v>0.3491</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.768</v>
+        <v>-0.5588</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4091</v>
+        <v>-0.1999</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3589</v>
@@ -1624,10 +1624,10 @@
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6083</v>
+        <v>-0.3991</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9881</v>
+        <v>-0.7789</v>
       </c>
       <c r="U15" t="n">
         <v>0.3798</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1006</v>
+        <v>-3.2366</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0664</v>
+        <v>-2.1579</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0341</v>
+        <v>-1.0787</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.8686</v>
+        <v>0.1682</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.8951</v>
+        <v>0.8208</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0265</v>
+        <v>-0.6525</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.489</v>
+        <v>1.38</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.3967</v>
+        <v>2.0118</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9077</v>
+        <v>-0.6318</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3797</v>
+        <v>-1.2117</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4985</v>
+        <v>-1.191</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1188</v>
+        <v>-0.0207</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8214</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6367</v>
+        <v>-1.7067</v>
       </c>
       <c r="T16" t="n">
-        <v>0.209</v>
+        <v>-1.1354</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4277</v>
+        <v>-0.5713</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3101</v>
+        <v>-1.6981</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0698</v>
+        <v>-1.349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.8468</v>
+        <v>-3.4239</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4717</v>
+        <v>-2.5894</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3751</v>
+        <v>-0.8345</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1682</v>
+        <v>-3.8686</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8208</v>
+        <v>-4.8951</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6525</v>
+        <v>1.0265</v>
       </c>
       <c r="J17" t="n">
-        <v>1.38</v>
+        <v>-1.489</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0118</v>
+        <v>-2.3967</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6318</v>
+        <v>0.9077</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2117</v>
+        <v>-2.3797</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.191</v>
+        <v>-2.4985</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0207</v>
+        <v>0.1188</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.3169</v>
+        <v>-0.6867</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4492</v>
+        <v>-0.314</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8677</v>
+        <v>-0.3727</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6981</v>
+        <v>0.3101</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.349</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0084</v>
+        <v>-3.9038</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4954</v>
+        <v>-3.3907</v>
       </c>
       <c r="F18" t="n">
         <v>-0.5131</v>
@@ -1858,10 +1858,10 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5424</v>
+        <v>-0.4378</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5928</v>
+        <v>-0.4882</v>
       </c>
       <c r="U18" t="n">
         <v>0.0504</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.3299</v>
+        <v>-7.0166</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.4169</v>
+        <v>-5.91</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9131</v>
+        <v>-1.1066</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.9658</v>
+        <v>-3.2803</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.6184</v>
+        <v>-2.7224</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6526</v>
+        <v>-0.5579</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.144</v>
+        <v>-0.3772</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.5383</v>
+        <v>0.1363</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3943</v>
+        <v>-0.5134</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8218</v>
+        <v>-2.9031</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.08</v>
+        <v>-2.8587</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2582</v>
+        <v>-0.0445</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.2855</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.1336</v>
+        <v>-4.1068</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0869</v>
+        <v>-1.2989</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.318</v>
+        <v>-1.426</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7689</v>
+        <v>0.1271</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0082</v>
+        <v>-0.5893</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1704</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.7018</v>
+        <v>-7.5129</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.3284</v>
+        <v>-7.0445</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3734</v>
+        <v>-0.4684</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2803</v>
+        <v>-3.9658</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7224</v>
+        <v>-5.6184</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5579</v>
+        <v>1.6526</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3772</v>
+        <v>-2.144</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1363</v>
+        <v>-3.5383</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5134</v>
+        <v>1.3943</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9031</v>
+        <v>-1.8218</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.8587</v>
+        <v>-2.08</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0445</v>
+        <v>0.2582</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8481</v>
+        <v>-3.2855</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1068</v>
+        <v>-5.1336</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9841</v>
+        <v>-1.2699</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8444</v>
+        <v>-0.9456</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1397</v>
+        <v>-0.3243</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5893</v>
+        <v>1.0082</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5893</v>
+        <v>-0.1704</v>
       </c>
     </row>
     <row r="21">
@@ -2050,7 +2050,7 @@
         <v>-16.1207</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.1853</v>
+        <v>-14.1852</v>
       </c>
       <c r="F21" t="n">
         <v>-1.9354</v>
@@ -2068,7 +2068,7 @@
         <v>7.464899999999998</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.570099999999999</v>
+        <v>-1.5701</v>
       </c>
       <c r="L21" t="n">
         <v>9.0352</v>
@@ -2095,10 +2095,10 @@
         <v>-8.175000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-7.711499999999999</v>
+        <v>-7.7115</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4635000000000001</v>
+        <v>-0.4636</v>
       </c>
       <c r="V21" t="n">
         <v>1.0248</v>
